--- a/templates/勤怠表雛形_2025年版.xlsx
+++ b/templates/勤怠表雛形_2025年版.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/790f474c98d19aa5/デスクトップ/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tomo/Downloads/kinten 3/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{7F3E3CE1-0197-4A49-A303-BEAF49D45C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FE0FA1B-CBE9-4610-8793-4E8FDDC0B99B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6797E3B2-3FFD-6C48-BEC4-DA84BE23512E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="860" yWindow="740" windowWidth="23260" windowHeight="12460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="勤務表" sheetId="9" r:id="rId1"/>
@@ -19,125 +19,20 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">勤務表!$A$1:$I$55</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>m_yagi</author>
-  </authors>
-  <commentList>
-    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="ＭＳ Ｐゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t>氏名欄上の●月度を入力すると自動的に反映されます。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="ＭＳ Ｐゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t>氏名欄上の●月度を入力すると自動的に反映されます。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="ＭＳ Ｐゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t>深夜0時以降に勤務する場合には、終了時間に24を足して記入。
-(ex：AM5：00に終了した場合　「24+5＝29」　と入力)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="ＭＳ Ｐゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t>控除時間は「1.0」を入力。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="ＭＳ Ｐゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t>自動計算</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="ＭＳ Ｐゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t>現場移動交通費を入力。その際、定期区間分を差し引いた金額を記入すること!
-タクシー等領収書が発生した場合は、必ず原本を郵送。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="ＭＳ Ｐゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t>経費発生の理由及び経費発生に関する経路を記入。
-(ex：セキュリティ研修の為　渋谷⇔日比谷※往復)</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -377,7 +272,7 @@
     <numFmt numFmtId="177" formatCode="d"/>
     <numFmt numFmtId="178" formatCode="\(@\)"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -452,14 +347,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0" tint="-0.249977111117893"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -932,20 +819,20 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -974,11 +861,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="6" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="6" fontId="3" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="6" fontId="3" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="6" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="6" fontId="3" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="6" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -988,13 +905,8 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="6" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="6" fontId="3" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="6" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -1003,31 +915,6 @@
     <xf numFmtId="6" fontId="3" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="6" fontId="3" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="6" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="6" fontId="3" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1355,40 +1242,40 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:I99"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="9.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="2" width="4.44140625" style="1" customWidth="1"/>
+    <col min="1" max="2" width="4.5" style="1" customWidth="1"/>
     <col min="3" max="11" width="12.6640625" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="15" customHeight="1">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
     </row>
     <row r="3" spans="1:9" ht="15" customHeight="1">
-      <c r="A3" s="57"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-    </row>
-    <row r="4" spans="1:9" s="3" customFormat="1" ht="14.4">
+      <c r="A3" s="58"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+    </row>
+    <row r="4" spans="1:9" s="3" customFormat="1" ht="15">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1419,21 +1306,21 @@
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
-      <c r="F6" s="49" t="s">
+      <c r="F6" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" ht="14.25" customHeight="1">
       <c r="C7" s="23"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" ht="14.25" customHeight="1">
       <c r="C8" s="23"/>
@@ -1464,10 +1351,10 @@
       <c r="G10" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="62" t="s">
+      <c r="H10" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="I10" s="63"/>
+      <c r="I10" s="53"/>
     </row>
     <row r="11" spans="1:9" s="8" customFormat="1" ht="18" customHeight="1" thickTop="1">
       <c r="A11" s="30">
@@ -1486,8 +1373,8 @@
         <v>0</v>
       </c>
       <c r="G11" s="14"/>
-      <c r="H11" s="60"/>
-      <c r="I11" s="61"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="55"/>
     </row>
     <row r="12" spans="1:9" s="8" customFormat="1" ht="18" customHeight="1">
       <c r="A12" s="31">
@@ -1506,8 +1393,8 @@
         <v>0</v>
       </c>
       <c r="G12" s="15"/>
-      <c r="H12" s="53"/>
-      <c r="I12" s="54"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="57"/>
     </row>
     <row r="13" spans="1:9" s="8" customFormat="1" ht="18" customHeight="1">
       <c r="A13" s="31">
@@ -1526,8 +1413,8 @@
         <v>0</v>
       </c>
       <c r="G13" s="14"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="61"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="55"/>
     </row>
     <row r="14" spans="1:9" s="8" customFormat="1" ht="18" customHeight="1">
       <c r="A14" s="31">
@@ -1546,8 +1433,8 @@
         <v>0</v>
       </c>
       <c r="G14" s="15"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="61"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="55"/>
     </row>
     <row r="15" spans="1:9" s="8" customFormat="1" ht="18" customHeight="1">
       <c r="A15" s="31">
@@ -1566,8 +1453,8 @@
         <v>0</v>
       </c>
       <c r="G15" s="14"/>
-      <c r="H15" s="53"/>
-      <c r="I15" s="54"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="57"/>
     </row>
     <row r="16" spans="1:9" s="8" customFormat="1" ht="18" customHeight="1">
       <c r="A16" s="31">
@@ -1586,8 +1473,8 @@
         <v>0</v>
       </c>
       <c r="G16" s="15"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="52"/>
+      <c r="H16" s="59"/>
+      <c r="I16" s="60"/>
     </row>
     <row r="17" spans="1:9" s="8" customFormat="1" ht="18" customHeight="1">
       <c r="A17" s="31">
@@ -1606,8 +1493,8 @@
         <v>0</v>
       </c>
       <c r="G17" s="15"/>
-      <c r="H17" s="58"/>
-      <c r="I17" s="59"/>
+      <c r="H17" s="49"/>
+      <c r="I17" s="50"/>
     </row>
     <row r="18" spans="1:9" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A18" s="31">
@@ -1626,8 +1513,8 @@
         <v>0</v>
       </c>
       <c r="G18" s="15"/>
-      <c r="H18" s="58"/>
-      <c r="I18" s="59"/>
+      <c r="H18" s="49"/>
+      <c r="I18" s="50"/>
     </row>
     <row r="19" spans="1:9" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A19" s="31">
@@ -1646,8 +1533,8 @@
         <v>0</v>
       </c>
       <c r="G19" s="15"/>
-      <c r="H19" s="58"/>
-      <c r="I19" s="59"/>
+      <c r="H19" s="49"/>
+      <c r="I19" s="50"/>
     </row>
     <row r="20" spans="1:9" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A20" s="31">
@@ -1666,8 +1553,8 @@
         <v>0</v>
       </c>
       <c r="G20" s="15"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="59"/>
+      <c r="H20" s="49"/>
+      <c r="I20" s="50"/>
     </row>
     <row r="21" spans="1:9" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A21" s="31">
@@ -1686,8 +1573,8 @@
         <v>0</v>
       </c>
       <c r="G21" s="14"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="54"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="57"/>
     </row>
     <row r="22" spans="1:9" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A22" s="31">
@@ -1706,8 +1593,8 @@
         <v>0</v>
       </c>
       <c r="G22" s="15"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="52"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="60"/>
     </row>
     <row r="23" spans="1:9" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A23" s="31">
@@ -1726,8 +1613,8 @@
         <v>0</v>
       </c>
       <c r="G23" s="15"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="52"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="60"/>
     </row>
     <row r="24" spans="1:9" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A24" s="31">
@@ -1746,8 +1633,8 @@
         <v>0</v>
       </c>
       <c r="G24" s="15"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="52"/>
+      <c r="H24" s="59"/>
+      <c r="I24" s="60"/>
     </row>
     <row r="25" spans="1:9" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A25" s="31">
@@ -1766,8 +1653,8 @@
         <v>0</v>
       </c>
       <c r="G25" s="15"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="52"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="60"/>
     </row>
     <row r="26" spans="1:9" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A26" s="31">
@@ -1786,8 +1673,8 @@
         <v>0</v>
       </c>
       <c r="G26" s="15"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="52"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="60"/>
     </row>
     <row r="27" spans="1:9" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A27" s="31">
@@ -1806,8 +1693,8 @@
         <v>0</v>
       </c>
       <c r="G27" s="15"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="52"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="60"/>
     </row>
     <row r="28" spans="1:9" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A28" s="31">
@@ -1826,8 +1713,8 @@
         <v>0</v>
       </c>
       <c r="G28" s="15"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="52"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="60"/>
     </row>
     <row r="29" spans="1:9" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A29" s="31">
@@ -1846,8 +1733,8 @@
         <v>0</v>
       </c>
       <c r="G29" s="14"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="52"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="60"/>
     </row>
     <row r="30" spans="1:9" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A30" s="31">
@@ -1866,8 +1753,8 @@
         <v>0</v>
       </c>
       <c r="G30" s="15"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="52"/>
+      <c r="H30" s="59"/>
+      <c r="I30" s="60"/>
     </row>
     <row r="31" spans="1:9" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A31" s="31">
@@ -1886,8 +1773,8 @@
         <v>0</v>
       </c>
       <c r="G31" s="15"/>
-      <c r="H31" s="51"/>
-      <c r="I31" s="52"/>
+      <c r="H31" s="59"/>
+      <c r="I31" s="60"/>
     </row>
     <row r="32" spans="1:9" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A32" s="31">
@@ -1906,8 +1793,8 @@
         <v>0</v>
       </c>
       <c r="G32" s="15"/>
-      <c r="H32" s="51"/>
-      <c r="I32" s="52"/>
+      <c r="H32" s="59"/>
+      <c r="I32" s="60"/>
     </row>
     <row r="33" spans="1:9" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A33" s="31">
@@ -1926,8 +1813,8 @@
         <v>0</v>
       </c>
       <c r="G33" s="15"/>
-      <c r="H33" s="51"/>
-      <c r="I33" s="52"/>
+      <c r="H33" s="59"/>
+      <c r="I33" s="60"/>
     </row>
     <row r="34" spans="1:9" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A34" s="31">
@@ -1946,8 +1833,8 @@
         <v>0</v>
       </c>
       <c r="G34" s="14"/>
-      <c r="H34" s="53"/>
-      <c r="I34" s="54"/>
+      <c r="H34" s="56"/>
+      <c r="I34" s="57"/>
     </row>
     <row r="35" spans="1:9" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A35" s="31">
@@ -1966,8 +1853,8 @@
         <v>0</v>
       </c>
       <c r="G35" s="14"/>
-      <c r="H35" s="53"/>
-      <c r="I35" s="54"/>
+      <c r="H35" s="56"/>
+      <c r="I35" s="57"/>
     </row>
     <row r="36" spans="1:9" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A36" s="31">
@@ -1986,8 +1873,8 @@
         <v>0</v>
       </c>
       <c r="G36" s="15"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="52"/>
+      <c r="H36" s="59"/>
+      <c r="I36" s="60"/>
     </row>
     <row r="37" spans="1:9" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A37" s="31">
@@ -2006,8 +1893,8 @@
         <v>0</v>
       </c>
       <c r="G37" s="15"/>
-      <c r="H37" s="51"/>
-      <c r="I37" s="52"/>
+      <c r="H37" s="59"/>
+      <c r="I37" s="60"/>
     </row>
     <row r="38" spans="1:9" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A38" s="31">
@@ -2026,8 +1913,8 @@
         <v>0</v>
       </c>
       <c r="G38" s="15"/>
-      <c r="H38" s="51"/>
-      <c r="I38" s="52"/>
+      <c r="H38" s="59"/>
+      <c r="I38" s="60"/>
     </row>
     <row r="39" spans="1:9" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A39" s="31">
@@ -2046,8 +1933,8 @@
         <v>0</v>
       </c>
       <c r="G39" s="15"/>
-      <c r="H39" s="51"/>
-      <c r="I39" s="52"/>
+      <c r="H39" s="59"/>
+      <c r="I39" s="60"/>
     </row>
     <row r="40" spans="1:9" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A40" s="31">
@@ -2066,8 +1953,8 @@
         <v>0</v>
       </c>
       <c r="G40" s="14"/>
-      <c r="H40" s="53"/>
-      <c r="I40" s="54"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="57"/>
     </row>
     <row r="41" spans="1:9" s="3" customFormat="1" ht="18" customHeight="1" thickBot="1">
       <c r="A41" s="32">
@@ -2086,10 +1973,10 @@
         <v>0</v>
       </c>
       <c r="G41" s="16"/>
-      <c r="H41" s="55"/>
-      <c r="I41" s="56"/>
-    </row>
-    <row r="42" spans="1:9" ht="10.199999999999999" thickBot="1"/>
+      <c r="H41" s="62"/>
+      <c r="I41" s="63"/>
+    </row>
+    <row r="42" spans="1:9" ht="13" thickBot="1"/>
     <row r="43" spans="1:9" ht="18" customHeight="1">
       <c r="D43" s="27"/>
       <c r="G43" s="24"/>
@@ -2126,46 +2013,46 @@
     <row r="47" spans="1:9">
       <c r="C47" s="28"/>
       <c r="D47" s="28"/>
-      <c r="H47" s="49" t="s">
+      <c r="H47" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="I47" s="49" t="s">
+      <c r="I47" s="51" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="C48" s="28"/>
       <c r="D48" s="28"/>
-      <c r="H48" s="49"/>
-      <c r="I48" s="49"/>
+      <c r="H48" s="51"/>
+      <c r="I48" s="51"/>
     </row>
     <row r="49" spans="3:9">
       <c r="C49" s="28"/>
       <c r="D49" s="28"/>
-      <c r="H49" s="50"/>
-      <c r="I49" s="50"/>
+      <c r="H49" s="61"/>
+      <c r="I49" s="61"/>
     </row>
     <row r="50" spans="3:9">
       <c r="C50" s="29"/>
       <c r="D50" s="28"/>
-      <c r="H50" s="50"/>
-      <c r="I50" s="50"/>
+      <c r="H50" s="61"/>
+      <c r="I50" s="61"/>
     </row>
     <row r="51" spans="3:9">
       <c r="C51" s="28"/>
       <c r="D51" s="28"/>
-      <c r="H51" s="50"/>
-      <c r="I51" s="50"/>
+      <c r="H51" s="61"/>
+      <c r="I51" s="61"/>
     </row>
     <row r="52" spans="3:9">
       <c r="C52" s="28"/>
       <c r="D52" s="28"/>
-      <c r="H52" s="50"/>
-      <c r="I52" s="50"/>
+      <c r="H52" s="61"/>
+      <c r="I52" s="61"/>
     </row>
     <row r="53" spans="3:9">
-      <c r="H53" s="50"/>
-      <c r="I53" s="50"/>
+      <c r="H53" s="61"/>
+      <c r="I53" s="61"/>
     </row>
     <row r="56" spans="3:9">
       <c r="C56" s="34"/>
@@ -2174,7 +2061,7 @@
       </c>
       <c r="E56" s="34"/>
     </row>
-    <row r="57" spans="3:9" ht="13.2">
+    <row r="57" spans="3:9" ht="14">
       <c r="C57" s="47">
         <v>45658</v>
       </c>
@@ -2185,7 +2072,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="58" spans="3:9" ht="13.2">
+    <row r="58" spans="3:9" ht="14">
       <c r="C58" s="47">
         <v>45670</v>
       </c>
@@ -2196,7 +2083,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="59" spans="3:9" ht="13.2">
+    <row r="59" spans="3:9" ht="14">
       <c r="C59" s="47">
         <v>45699</v>
       </c>
@@ -2207,7 +2094,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="60" spans="3:9" ht="13.2">
+    <row r="60" spans="3:9" ht="14">
       <c r="C60" s="47">
         <v>45711</v>
       </c>
@@ -2218,7 +2105,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="61" spans="3:9" ht="13.2">
+    <row r="61" spans="3:9" ht="14">
       <c r="C61" s="47">
         <v>45712</v>
       </c>
@@ -2229,7 +2116,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="62" spans="3:9" ht="13.2">
+    <row r="62" spans="3:9" ht="14">
       <c r="C62" s="47">
         <v>45736</v>
       </c>
@@ -2240,7 +2127,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="63" spans="3:9" ht="13.2">
+    <row r="63" spans="3:9" ht="14">
       <c r="C63" s="47">
         <v>45776</v>
       </c>
@@ -2251,7 +2138,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="64" spans="3:9" ht="13.2">
+    <row r="64" spans="3:9" ht="14">
       <c r="C64" s="47">
         <v>45780</v>
       </c>
@@ -2262,7 +2149,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="3:8" ht="13.2">
+    <row r="65" spans="3:8" ht="14">
       <c r="C65" s="47">
         <v>45781</v>
       </c>
@@ -2273,7 +2160,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="66" spans="3:8" ht="13.2">
+    <row r="66" spans="3:8" ht="14">
       <c r="C66" s="47">
         <v>45782</v>
       </c>
@@ -2284,7 +2171,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="3:8" ht="13.2">
+    <row r="67" spans="3:8" ht="14">
       <c r="C67" s="47">
         <v>45783</v>
       </c>
@@ -2295,7 +2182,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="68" spans="3:8" ht="13.2">
+    <row r="68" spans="3:8" ht="14">
       <c r="C68" s="47">
         <v>45859</v>
       </c>
@@ -2306,7 +2193,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="3:8" ht="13.2">
+    <row r="69" spans="3:8" ht="14">
       <c r="C69" s="47">
         <v>45880</v>
       </c>
@@ -2317,7 +2204,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="70" spans="3:8" ht="13.2">
+    <row r="70" spans="3:8" ht="14">
       <c r="C70" s="47">
         <v>45915</v>
       </c>
@@ -2328,7 +2215,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="71" spans="3:8" ht="13.2">
+    <row r="71" spans="3:8" ht="14">
       <c r="C71" s="47">
         <v>45923</v>
       </c>
@@ -2339,7 +2226,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="72" spans="3:8" ht="13.2">
+    <row r="72" spans="3:8" ht="14">
       <c r="C72" s="47">
         <v>45943</v>
       </c>
@@ -2350,7 +2237,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="73" spans="3:8" ht="13.2">
+    <row r="73" spans="3:8" ht="14">
       <c r="C73" s="47">
         <v>45964</v>
       </c>
@@ -2361,7 +2248,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="74" spans="3:8" ht="13.2">
+    <row r="74" spans="3:8" ht="14">
       <c r="C74" s="47">
         <v>45984</v>
       </c>
@@ -2372,7 +2259,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="3:8" ht="13.2">
+    <row r="75" spans="3:8" ht="14">
       <c r="C75" s="47">
         <v>45985</v>
       </c>
@@ -2383,145 +2270,145 @@
         <v>34</v>
       </c>
     </row>
-    <row r="76" spans="3:8" ht="13.8">
+    <row r="76" spans="3:8" ht="14">
       <c r="C76" s="36"/>
       <c r="D76" s="37"/>
       <c r="E76" s="39"/>
       <c r="H76" s="38"/>
     </row>
-    <row r="77" spans="3:8" ht="13.8">
+    <row r="77" spans="3:8" ht="14">
       <c r="C77" s="36"/>
       <c r="D77" s="41"/>
       <c r="E77" s="40"/>
       <c r="H77" s="38"/>
     </row>
-    <row r="78" spans="3:8" ht="13.8">
+    <row r="78" spans="3:8" ht="14">
       <c r="C78" s="36"/>
       <c r="D78" s="41"/>
       <c r="E78" s="40"/>
       <c r="H78" s="38"/>
     </row>
-    <row r="79" spans="3:8" ht="13.8">
+    <row r="79" spans="3:8" ht="14">
       <c r="C79" s="36"/>
       <c r="D79" s="41"/>
       <c r="E79" s="40"/>
       <c r="H79" s="38"/>
     </row>
-    <row r="80" spans="3:8" ht="13.8">
+    <row r="80" spans="3:8" ht="14">
       <c r="C80" s="36"/>
       <c r="D80" s="41"/>
       <c r="E80" s="40"/>
       <c r="H80" s="38"/>
     </row>
-    <row r="81" spans="3:8" ht="13.8">
+    <row r="81" spans="3:8" ht="14">
       <c r="C81" s="36"/>
       <c r="D81" s="41"/>
       <c r="E81" s="40"/>
       <c r="H81" s="38"/>
     </row>
-    <row r="82" spans="3:8" ht="13.8">
+    <row r="82" spans="3:8" ht="14">
       <c r="C82" s="36"/>
       <c r="D82" s="41"/>
       <c r="E82" s="40"/>
       <c r="H82" s="38"/>
     </row>
-    <row r="83" spans="3:8" ht="13.8">
+    <row r="83" spans="3:8" ht="14">
       <c r="C83" s="36"/>
       <c r="D83" s="41"/>
       <c r="E83" s="40"/>
       <c r="H83" s="38"/>
     </row>
-    <row r="84" spans="3:8" ht="13.8">
+    <row r="84" spans="3:8" ht="14">
       <c r="C84" s="36"/>
       <c r="D84" s="41"/>
       <c r="E84" s="40"/>
       <c r="H84" s="38"/>
     </row>
-    <row r="85" spans="3:8" ht="13.8">
+    <row r="85" spans="3:8" ht="14">
       <c r="C85" s="36"/>
       <c r="D85" s="41"/>
       <c r="E85" s="40"/>
       <c r="H85" s="38"/>
     </row>
-    <row r="86" spans="3:8" ht="13.8">
+    <row r="86" spans="3:8" ht="14">
       <c r="C86" s="36"/>
       <c r="D86" s="41"/>
       <c r="E86" s="40"/>
       <c r="H86" s="38"/>
     </row>
-    <row r="87" spans="3:8" ht="13.8">
+    <row r="87" spans="3:8" ht="14">
       <c r="C87" s="36"/>
       <c r="D87" s="41"/>
       <c r="E87" s="40"/>
       <c r="H87" s="38"/>
     </row>
-    <row r="88" spans="3:8" ht="13.8">
+    <row r="88" spans="3:8" ht="14">
       <c r="C88" s="36"/>
       <c r="D88" s="41"/>
       <c r="E88" s="40"/>
       <c r="H88" s="38"/>
     </row>
-    <row r="89" spans="3:8" ht="13.8">
+    <row r="89" spans="3:8" ht="14">
       <c r="C89" s="36"/>
       <c r="D89" s="41"/>
       <c r="E89" s="40"/>
       <c r="H89" s="38"/>
     </row>
-    <row r="90" spans="3:8" ht="13.8">
+    <row r="90" spans="3:8" ht="14">
       <c r="C90" s="36"/>
       <c r="D90" s="41"/>
       <c r="E90" s="40"/>
       <c r="H90" s="38"/>
     </row>
-    <row r="91" spans="3:8" ht="13.8">
+    <row r="91" spans="3:8" ht="14">
       <c r="C91" s="36"/>
       <c r="D91" s="41"/>
       <c r="E91" s="40"/>
       <c r="H91" s="38"/>
     </row>
-    <row r="92" spans="3:8" ht="13.8">
+    <row r="92" spans="3:8" ht="14">
       <c r="C92" s="36"/>
       <c r="D92" s="41"/>
       <c r="E92" s="40"/>
       <c r="H92" s="38"/>
     </row>
-    <row r="93" spans="3:8" ht="13.8">
+    <row r="93" spans="3:8" ht="14">
       <c r="C93" s="36"/>
       <c r="D93" s="41"/>
       <c r="E93" s="40"/>
       <c r="H93" s="38"/>
     </row>
-    <row r="94" spans="3:8" ht="13.8">
+    <row r="94" spans="3:8" ht="14">
       <c r="C94" s="36"/>
       <c r="D94" s="41"/>
       <c r="E94" s="40"/>
       <c r="H94" s="38"/>
     </row>
-    <row r="95" spans="3:8" ht="13.8">
+    <row r="95" spans="3:8" ht="14">
       <c r="C95" s="36"/>
       <c r="D95" s="41"/>
       <c r="E95" s="40"/>
       <c r="H95" s="38"/>
     </row>
-    <row r="96" spans="3:8" ht="13.8">
+    <row r="96" spans="3:8" ht="14">
       <c r="C96" s="36"/>
       <c r="D96" s="41"/>
       <c r="E96" s="40"/>
       <c r="H96" s="38"/>
     </row>
-    <row r="97" spans="3:8" ht="13.8">
+    <row r="97" spans="3:8" ht="14">
       <c r="C97" s="36"/>
       <c r="D97" s="41"/>
       <c r="E97" s="40"/>
       <c r="H97" s="38"/>
     </row>
-    <row r="98" spans="3:8" ht="13.8">
+    <row r="98" spans="3:8" ht="14">
       <c r="C98" s="36"/>
       <c r="D98" s="41"/>
       <c r="E98" s="40"/>
       <c r="H98" s="38"/>
     </row>
-    <row r="99" spans="3:8" ht="13.8">
+    <row r="99" spans="3:8" ht="14">
       <c r="C99" s="36"/>
       <c r="D99" s="41"/>
       <c r="E99" s="40"/>
@@ -2529,14 +2416,21 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:I7"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="H49:H53"/>
+    <mergeCell ref="I49:I53"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="H36:I36"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="H34:I34"/>
     <mergeCell ref="H26:I26"/>
@@ -2553,21 +2447,14 @@
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="H17:I17"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="H49:H53"/>
-    <mergeCell ref="I49:I53"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:I7"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H13:I13"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="B11:B41">
@@ -2583,11 +2470,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.39370078740157483" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup paperSize="9" scale="95" orientation="portrait" horizontalDpi="400" verticalDpi="400" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="86" orientation="portrait" horizontalDpi="400" verticalDpi="400" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="55" max="8" man="1"/>
-  </rowBreaks>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>